--- a/artfynd/A 38053-2024 artfynd.xlsx
+++ b/artfynd/A 38053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133217974</v>
+        <v>133217951</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586397</v>
+        <v>586400</v>
       </c>
       <c r="R2" t="n">
-        <v>7011081</v>
+        <v>7011099</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>133217973</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133217951</v>
+        <v>133217977</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högkälen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586400</v>
+        <v>586231</v>
       </c>
       <c r="R4" t="n">
-        <v>7011099</v>
+        <v>7011041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avbarkningar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1003,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133217974</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högkälen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>586397</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7011081</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38053-2024 artfynd.xlsx
+++ b/artfynd/A 38053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217977</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>